--- a/Donnees/Statistiques Démographiques et sociales/Santé/Theme_Santé (2).xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Santé/Theme_Santé (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Santé\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B716D534-DCC6-4410-ADC7-6B4BBF0C3E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A15CC1-60DE-4E84-8E78-4A164D03146D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,10 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="81">
-  <si>
-    <t>Tableau 1.3.1 : Evolution du nombre de centres de santé par Wilaya durant la période 2014-2024</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="80">
   <si>
     <t>2014</t>
   </si>
@@ -63,12 +60,6 @@
     <t>2024</t>
   </si>
   <si>
-    <t>Tableau 1.3.2 : Evolution du nombre de postes de santé par Wilaya durant la période 2014-2024</t>
-  </si>
-  <si>
-    <t>Tableau 1.3.3: Pourcentage de femmes de 15-49 ans qui ont reçu des soins prénatals durant la grossesse par wilaya selon le type du personnel de santé consulté</t>
-  </si>
-  <si>
     <t>Prestataire de soins prénatals~Gynécologue-médecin</t>
   </si>
   <si>
@@ -96,9 +87,6 @@
     <t>Source:  ANSADE,  EDSM 2019-2021</t>
   </si>
   <si>
-    <t>Tableau 1.3.4: Pourcentage de femmes 15-49 ans qui ont effectué au moins 4 visites prénatales dont au moins une avec un prestataire de santé qualifié par wilaya selon la qualité des soins prénatals effectué.</t>
-  </si>
-  <si>
     <t>Qualité des soins prénatals~Pourcentage ayant effectué au moins quatre visites prénatales dont au moins une dispensée par un prestataire qualifié</t>
   </si>
   <si>
@@ -108,30 +96,9 @@
     <t>Qualité des soins prénatals~Pourcentage ayant effectué au moins 4 visites prénatales et tous les examens de base du suivi prénatal</t>
   </si>
   <si>
-    <t>Tableau 1.3.5: Répartition (en %) des naissances vivantes ayant eu lieu au cours des 5 années ayant précédé l'enquête (EDSM) par Wilaya selon le lieu de l'accouchement</t>
-  </si>
-  <si>
-    <t>Etablissement de santé~Secteur public</t>
-  </si>
-  <si>
-    <t>Etablissement de santé~Secteur privé</t>
-  </si>
-  <si>
-    <t>Etablissement de santé~Maison</t>
-  </si>
-  <si>
-    <t>Etablissement de santé~Autre</t>
-  </si>
-  <si>
-    <t>Etablissement de santé~Total</t>
-  </si>
-  <si>
     <t>Pourcentage dont l'accouchement s'est déroulé dans un établissement de  santé</t>
   </si>
   <si>
-    <t>Tableau 1.3.6: Répartition (en %) des naissances vivantes ayant eu lieu au cours des 5 années ayant précédé l'enquête (EDSM) par Wilaya selon le type de personnel ayant assisté l'accouchement,</t>
-  </si>
-  <si>
     <t>Personne ayant assisté l'accouchement~Gynécologue-médecin</t>
   </si>
   <si>
@@ -150,18 +117,12 @@
     <t>Personne ayant assisté l'accouchement~Autre</t>
   </si>
   <si>
-    <t>Personne ayant assisté l'accouchement~Personne</t>
-  </si>
-  <si>
     <t>Personne ayant assisté l'accouchement~Total</t>
   </si>
   <si>
     <t>Pourcentage dont l'accouchement a été assisté par un prestataire qualifié</t>
   </si>
   <si>
-    <t>Tableau 1.3.7: Pourcentage de naissances vivantes ayant eu lieu au cours des 5 dernières années ayant précédé l'enquête (EDSM) accouchées par césarienne par Wilaya selon le moment de la prise de décision</t>
-  </si>
-  <si>
     <t>Moment de la décision de mener une césarienne~Décidée avant le début des douleurs</t>
   </si>
   <si>
@@ -180,42 +141,6 @@
     <t>Aucun vaccin</t>
   </si>
   <si>
-    <t>Tableau 1.3.9: Pourcentage d’enfants de moins de 5 ans par Wilaya selon les trois indices anthropométriques de mesure de l’état nutritionnel : la taille-pour-âge, le poids-pour-taille et le poids-pour-âge,</t>
-  </si>
-  <si>
-    <t>Taille-pour-Âge1~Pourcen­tage en dessous de -3 ET</t>
-  </si>
-  <si>
-    <t>Taille-pour-Âge1~Pourcen­tage en dessous de -2 ET2</t>
-  </si>
-  <si>
-    <t>Taille-pour-Âge1~Score centré réduit moyen (ET)</t>
-  </si>
-  <si>
-    <t>Poids-pour-Taille~Pourcen­tage en dessous de -3 ET</t>
-  </si>
-  <si>
-    <t>Poids-pour-Taille~Pourcen­tage en dessous de -2 ET2</t>
-  </si>
-  <si>
-    <t>Poids-pour-Taille~Pourcen­tage au-dessus de +2 ET</t>
-  </si>
-  <si>
-    <t>Poids-pour-Taille~Score centré réduit moyen (ET)</t>
-  </si>
-  <si>
-    <t>Poids-pour-Âge~Pourcen­tage en dessous de -3 ET</t>
-  </si>
-  <si>
-    <t>Poids-pour-Âge~Pourcen­tage en dessous de -2 ET2</t>
-  </si>
-  <si>
-    <t>Poids-pour-Âge~Pourcen­tage au-dessus de +2 ET</t>
-  </si>
-  <si>
-    <t>Poids-pour-Âge~Score centré réduit moyen (ET)</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -252,9 +177,6 @@
     <t>Wilaya~Guidimakha</t>
   </si>
   <si>
-    <t>Wilaya~Tiris-Zemmour</t>
-  </si>
-  <si>
     <t>Wilaya~Inchiri</t>
   </si>
   <si>
@@ -270,7 +192,82 @@
     <t>Wilaya~Nouakchott-Sud</t>
   </si>
   <si>
-    <t>Wilaya~Nouakchott Sud</t>
+    <t>Tableau 1.3.1 : Evolution du nombre de centres de santé par wilaya  2014-2024</t>
+  </si>
+  <si>
+    <t>Wilaya~Tiris Zemmour</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.2 : Evolution du nombre de postes de santé par wilaya  2014-2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.3: Pourcentage de femmes de 15-49 ans ayant reçu des soins prénatals durant la grossesse par wilaya selon le type de personnel de santé consulté</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.4: Pourcentage de femmes 15-49 ans ayant effectué au moins 4 visites prénatales dont au moins une avec un prestataire de santé qualifié par wilaya et selon la qualité des soins prénatals réalisé</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.5: Répartition (en %) des naissances vivantes ayant eu lieu au cours des 5 années précédant l'enquête (EDSM) par wilaya et selon le lieu de l'accouchement</t>
+  </si>
+  <si>
+    <t>Lieu de l'accouchement~Maison</t>
+  </si>
+  <si>
+    <t>Lieu de l'accouchement~Autre</t>
+  </si>
+  <si>
+    <t>Lieu de l'accouchement~Total</t>
+  </si>
+  <si>
+    <t>Lieu de l'accouchement~Etablissement de santé public</t>
+  </si>
+  <si>
+    <t>Lieu de l'accouchement~Etablissement de santé privé</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.6: Répartition (en %) des naissances vivantes ayant eu lieu au cours des 5 années précédant l'enquête (EDSM) par wilaya et selon le type de personnel ayant assisté l'accouchement</t>
+  </si>
+  <si>
+    <t>Personne ayant assisté l'accouchement~Aucune</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.7: Pourcentage de naissances vivantes ayant eu lieu au cours des 5 dernières années précédant l'enquête (EDSM) accouchées par césarienne par wilaya et selon le moment de la prise de décision</t>
+  </si>
+  <si>
+    <t>Taille-pour-âge~Pourcen­tage en dessous de -3 ET</t>
+  </si>
+  <si>
+    <t>Taille-pour-âge~Pourcen­tage en dessous de -2 ET2</t>
+  </si>
+  <si>
+    <t>Taille-pour-âge~Score centré réduit moyen (ET)</t>
+  </si>
+  <si>
+    <t>Poids-pour-taille ~Pourcen­tage en dessous de -3ET</t>
+  </si>
+  <si>
+    <t>Poids-pour-taille ~Pourcen­tage en dessous de -2 ET2</t>
+  </si>
+  <si>
+    <t>Poids-pour-taille ~Pourcen­tage au-dessus de +2 ET</t>
+  </si>
+  <si>
+    <t>Poids-pour-taille ~Score centré réduit moyen (ET)</t>
+  </si>
+  <si>
+    <t>Tableau 1.3.9: Pourcentage d’enfants de moins de 5 ans par wilaya et selon les trois indices anthropométriques de mesure de l’état nutritionnel :  Taille-pour-âge, Poids-pour-taille  et Poids-pour-âge</t>
+  </si>
+  <si>
+    <t>Poids-pour-âge~Pourcen­tage en dessous de -3 ET</t>
+  </si>
+  <si>
+    <t>Poids-pour-âge~Pourcen­tage en dessous de -2 ET2</t>
+  </si>
+  <si>
+    <t>Poids-pour-âge~Pourcen­tage au-dessus de +2 ET</t>
+  </si>
+  <si>
+    <t>Poids-pour-âge~Score centré réduit moyen (ET)</t>
   </si>
 </sst>
 </file>
@@ -630,45 +627,45 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>90</v>
@@ -703,7 +700,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -738,7 +735,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -773,7 +770,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -808,7 +805,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -843,7 +840,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>11</v>
@@ -878,7 +875,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -913,7 +910,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -948,7 +945,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -983,7 +980,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -1018,7 +1015,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1053,7 +1050,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>4</v>
@@ -1088,7 +1085,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -1123,7 +1120,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1155,7 +1152,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -1187,7 +1184,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="C18">
         <v>9</v>
@@ -1219,7 +1216,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1237,45 +1234,45 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>588</v>
@@ -1310,7 +1307,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>124</v>
@@ -1345,7 +1342,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>62</v>
@@ -1380,7 +1377,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>82</v>
@@ -1415,7 +1412,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>53</v>
@@ -1450,7 +1447,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>78</v>
@@ -1485,7 +1482,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>91</v>
@@ -1520,7 +1517,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>27</v>
@@ -1555,7 +1552,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1590,7 +1587,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>24</v>
@@ -1625,7 +1622,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>40</v>
@@ -1660,7 +1657,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -1695,7 +1692,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B15">
         <v>4</v>
@@ -1730,7 +1727,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C16">
         <v>7</v>
@@ -1762,7 +1759,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="C17">
         <v>13</v>
@@ -1794,7 +1791,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="C18">
         <v>8</v>
@@ -1823,7 +1820,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1837,42 +1834,50 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
+    <col min="2" max="2" width="46" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="59.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="68" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>24.4</v>
@@ -1901,7 +1906,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>22.8</v>
@@ -1930,7 +1935,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>21.2</v>
@@ -1959,7 +1964,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>17.899999999999999</v>
@@ -1988,7 +1993,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>13.7</v>
@@ -2017,7 +2022,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>18.600000000000001</v>
@@ -2046,7 +2051,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>29.1</v>
@@ -2075,7 +2080,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>27.5</v>
@@ -2104,7 +2109,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>29.1</v>
@@ -2133,7 +2138,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>40.299999999999997</v>
@@ -2162,7 +2167,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>7.2</v>
@@ -2191,7 +2196,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>34.5</v>
@@ -2220,7 +2225,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>35</v>
@@ -2249,7 +2254,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <v>26</v>
@@ -2278,7 +2283,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>43.2</v>
@@ -2307,7 +2312,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>35.799999999999997</v>
@@ -2336,7 +2341,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2350,27 +2355,28 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="2" max="2" width="125.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>37.6</v>
@@ -2384,7 +2390,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>14.9</v>
@@ -2398,7 +2404,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>28.8</v>
@@ -2412,7 +2418,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>44.8</v>
@@ -2426,7 +2432,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>41.1</v>
@@ -2440,7 +2446,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>47</v>
@@ -2454,7 +2460,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>52.5</v>
@@ -2468,7 +2474,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>17.399999999999999</v>
@@ -2482,7 +2488,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>70.7</v>
@@ -2496,7 +2502,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>31.2</v>
@@ -2510,7 +2516,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>38.299999999999997</v>
@@ -2524,7 +2530,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>25.1</v>
@@ -2538,7 +2544,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>44.833333333333343</v>
@@ -2552,7 +2558,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <v>50.8</v>
@@ -2566,7 +2572,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>42.9</v>
@@ -2580,7 +2586,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>40.799999999999997</v>
@@ -2594,7 +2600,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2608,36 +2614,38 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
+    <col min="2" max="2" width="39.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>67.7</v>
@@ -2660,7 +2668,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>44.5</v>
@@ -2683,7 +2691,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>50.7</v>
@@ -2706,7 +2714,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>59.2</v>
@@ -2729,7 +2737,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>64.599999999999994</v>
@@ -2752,7 +2760,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>77.7</v>
@@ -2775,7 +2783,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>87.6</v>
@@ -2798,7 +2806,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>73.2</v>
@@ -2821,7 +2829,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>92.2</v>
@@ -2844,7 +2852,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>62.4</v>
@@ -2867,7 +2875,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>49.4</v>
@@ -2890,7 +2898,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>90.8</v>
@@ -2913,7 +2921,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>91.6</v>
@@ -2936,7 +2944,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <v>89.3</v>
@@ -2959,7 +2967,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>91.5</v>
@@ -2982,7 +2990,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>94.1</v>
@@ -3005,7 +3013,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3017,44 +3025,51 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="40.77734375" customWidth="1"/>
+    <col min="2" max="2" width="54.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="63.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>11.1</v>
@@ -3086,7 +3101,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>8.6</v>
@@ -3118,7 +3133,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>5.4</v>
@@ -3150,7 +3165,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>7.4</v>
@@ -3182,7 +3197,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>7.7</v>
@@ -3214,7 +3229,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>8.9</v>
@@ -3246,7 +3261,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>10.7</v>
@@ -3278,7 +3293,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>12.2</v>
@@ -3310,7 +3325,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>23.6</v>
@@ -3342,7 +3357,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>8.5</v>
@@ -3374,7 +3389,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>2.2000000000000002</v>
@@ -3406,7 +3421,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>23.3</v>
@@ -3438,7 +3453,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>20.066700000000001</v>
@@ -3470,7 +3485,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <v>16.600000000000001</v>
@@ -3502,7 +3517,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>28.8</v>
@@ -3534,7 +3549,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>14.8</v>
@@ -3566,7 +3581,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3584,23 +3599,23 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>3.2</v>
@@ -3614,7 +3629,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>0.4</v>
@@ -3628,7 +3643,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3642,7 +3657,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>2.1</v>
@@ -3656,7 +3671,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>0.2</v>
@@ -3670,7 +3685,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>2.6</v>
@@ -3684,7 +3699,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -3698,7 +3713,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>2.1</v>
@@ -3712,7 +3727,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>9</v>
@@ -3726,7 +3741,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>2.4</v>
@@ -3740,7 +3755,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>0.6</v>
@@ -3754,7 +3769,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>7.8</v>
@@ -3768,7 +3783,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>8.0666666666666682</v>
@@ -3782,7 +3797,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <v>7.2</v>
@@ -3796,7 +3811,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>11.4</v>
@@ -3810,7 +3825,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>5.6</v>
@@ -3824,7 +3839,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3839,20 +3854,20 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>37.9</v>
@@ -3863,7 +3878,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>23.1</v>
@@ -3874,7 +3889,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>47.1</v>
@@ -3885,7 +3900,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>38.299999999999997</v>
@@ -3896,7 +3911,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>39.799999999999997</v>
@@ -3907,7 +3922,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>43.1</v>
@@ -3918,7 +3933,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>25.6</v>
@@ -3929,7 +3944,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>54.3</v>
@@ -3940,7 +3955,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>36.9</v>
@@ -3951,7 +3966,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>29.8</v>
@@ -3962,7 +3977,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>49.1</v>
@@ -3973,7 +3988,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>42.4</v>
@@ -3984,7 +3999,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>34.9</v>
@@ -3995,7 +4010,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <v>28.3</v>
@@ -4006,7 +4021,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>48.6</v>
@@ -4017,7 +4032,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>27.9</v>
@@ -4028,7 +4043,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -4040,50 +4055,57 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B3">
         <v>8.6</v>
@@ -4121,7 +4143,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>14.2</v>
@@ -4159,7 +4181,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="B5">
         <v>9.9</v>
@@ -4197,7 +4219,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="B6">
         <v>8.1999999999999993</v>
@@ -4235,7 +4257,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B7">
         <v>10.4</v>
@@ -4273,7 +4295,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="B8">
         <v>5.5</v>
@@ -4311,7 +4333,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="B9">
         <v>7.2</v>
@@ -4349,7 +4371,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="B10">
         <v>11.4</v>
@@ -4387,7 +4409,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -4425,7 +4447,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="B12">
         <v>15.5</v>
@@ -4463,7 +4485,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="B13">
         <v>8.6999999999999993</v>
@@ -4501,7 +4523,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -4539,7 +4561,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B15">
         <v>5.0999999999999996</v>
@@ -4577,7 +4599,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B16">
         <v>4.2</v>
@@ -4615,7 +4637,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B17">
         <v>5.5</v>
@@ -4653,7 +4675,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B18">
         <v>5.6</v>
@@ -4691,7 +4713,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Donnees/Statistiques Démographiques et sociales/Santé/Theme_Santé (2).xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Santé/Theme_Santé (2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Santé\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A15CC1-60DE-4E84-8E78-4A164D03146D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7F98822-E5A5-4452-A293-812A0465CCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Centres de Santé" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="TS6" sheetId="8" r:id="rId8"/>
     <sheet name="ST7" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -84,9 +84,6 @@
     <t>Pourcentage ayant reçu des soins prénatals par un prestataire de santé qualifié</t>
   </si>
   <si>
-    <t>Source:  ANSADE,  EDSM 2019-2021</t>
-  </si>
-  <si>
     <t>Qualité des soins prénatals~Pourcentage ayant effectué au moins quatre visites prénatales dont au moins une dispensée par un prestataire qualifié</t>
   </si>
   <si>
@@ -144,9 +141,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Source : MS, Annuaires des Statistiques Sanitaires</t>
-  </si>
-  <si>
     <t>Wilaya~Hodh Charghi</t>
   </si>
   <si>
@@ -268,6 +262,12 @@
   </si>
   <si>
     <t>Poids-pour-âge~Score centré réduit moyen (ET)</t>
+  </si>
+  <si>
+    <t>Source : MS/Annuaires des Statistiques Sanitaires</t>
+  </si>
+  <si>
+    <t>Source:  ANSADE/EDSM 2019-2021</t>
   </si>
 </sst>
 </file>
@@ -627,7 +627,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -665,7 +665,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>90</v>
@@ -700,7 +700,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>9</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -770,7 +770,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -840,7 +840,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>11</v>
@@ -875,7 +875,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>7</v>
@@ -910,7 +910,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>4</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>8</v>
@@ -980,7 +980,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>4</v>
@@ -1015,7 +1015,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -1050,7 +1050,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>4</v>
@@ -1085,7 +1085,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B15">
         <v>2</v>
@@ -1120,7 +1120,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1152,7 +1152,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17">
         <v>7</v>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18">
         <v>9</v>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1234,7 +1234,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -1272,7 +1272,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>588</v>
@@ -1307,7 +1307,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>124</v>
@@ -1342,7 +1342,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>62</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>82</v>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>53</v>
@@ -1447,7 +1447,7 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>78</v>
@@ -1482,7 +1482,7 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>91</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>27</v>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -1587,7 +1587,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>24</v>
@@ -1622,7 +1622,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>40</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -1692,7 +1692,7 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B15">
         <v>4</v>
@@ -1727,7 +1727,7 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C16">
         <v>7</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17">
         <v>13</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C18">
         <v>8</v>
@@ -1820,7 +1820,7 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1846,7 +1846,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -1877,7 +1877,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>24.4</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>22.8</v>
@@ -1935,7 +1935,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>21.2</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>17.899999999999999</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>13.7</v>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>18.600000000000001</v>
@@ -2051,7 +2051,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>29.1</v>
@@ -2080,7 +2080,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>27.5</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>29.1</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>40.299999999999997</v>
@@ -2167,7 +2167,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>7.2</v>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>34.5</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>35</v>
@@ -2234,7 +2234,7 @@
         <v>61.5</v>
       </c>
       <c r="D15">
-        <v>0.83333333333333337</v>
+        <v>0.83333333333333304</v>
       </c>
       <c r="E15">
         <v>6.6666666666666666E-2</v>
@@ -2254,7 +2254,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>26</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>43.2</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>35.799999999999997</v>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2360,23 +2360,23 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>37.6</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>14.9</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>28.8</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>44.8</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>41.1</v>
@@ -2446,7 +2446,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>47</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>52.5</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>17.399999999999999</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>70.7</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>31.2</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>38.299999999999997</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>25.1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>44.833333333333343</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>50.8</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>42.9</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>40.799999999999997</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2620,32 +2620,32 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>67.7</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>44.5</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>50.7</v>
@@ -2714,7 +2714,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>59.2</v>
@@ -2737,7 +2737,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>64.599999999999994</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>77.7</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>87.6</v>
@@ -2806,7 +2806,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>73.2</v>
@@ -2829,7 +2829,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>92.2</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>62.4</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>49.4</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>90.8</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>91.6</v>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>89.3</v>
@@ -2967,7 +2967,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>91.5</v>
@@ -2990,7 +2990,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>94.1</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3035,41 +3035,41 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>11.1</v>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>8.6</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>5.4</v>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>7.4</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>7.7</v>
@@ -3229,7 +3229,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>8.9</v>
@@ -3261,7 +3261,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>10.7</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>12.2</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>23.6</v>
@@ -3357,7 +3357,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>8.5</v>
@@ -3389,7 +3389,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>2.2000000000000002</v>
@@ -3421,7 +3421,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>23.3</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>20.066700000000001</v>
@@ -3485,7 +3485,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>16.600000000000001</v>
@@ -3517,7 +3517,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>28.8</v>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>14.8</v>
@@ -3581,7 +3581,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3599,23 +3599,23 @@
   <sheetData>
     <row r="1" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>3.2</v>
@@ -3629,7 +3629,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>0.4</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -3657,7 +3657,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>2.1</v>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>0.2</v>
@@ -3685,7 +3685,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>2.6</v>
@@ -3699,7 +3699,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -3713,7 +3713,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>2.1</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>9</v>
@@ -3741,7 +3741,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>2.4</v>
@@ -3755,7 +3755,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>0.6</v>
@@ -3769,7 +3769,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>7.8</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>8.0666666666666682</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>7.2</v>
@@ -3811,7 +3811,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>11.4</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>5.6</v>
@@ -3839,7 +3839,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3854,20 +3854,20 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>37.9</v>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>23.1</v>
@@ -3889,7 +3889,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>47.1</v>
@@ -3900,7 +3900,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>38.299999999999997</v>
@@ -3911,7 +3911,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>39.799999999999997</v>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>43.1</v>
@@ -3933,7 +3933,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>25.6</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>54.3</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>36.9</v>
@@ -3966,7 +3966,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>29.8</v>
@@ -3977,7 +3977,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>49.1</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>42.4</v>
@@ -3999,7 +3999,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>34.9</v>
@@ -4010,7 +4010,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>28.3</v>
@@ -4021,7 +4021,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>48.6</v>
@@ -4032,7 +4032,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>27.9</v>
@@ -4043,7 +4043,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4065,47 +4065,47 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3">
         <v>8.6</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4">
         <v>14.2</v>
@@ -4181,7 +4181,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5">
         <v>9.9</v>
@@ -4219,7 +4219,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6">
         <v>8.1999999999999993</v>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7">
         <v>10.4</v>
@@ -4295,7 +4295,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8">
         <v>5.5</v>
@@ -4333,7 +4333,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9">
         <v>7.2</v>
@@ -4371,7 +4371,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10">
         <v>11.4</v>
@@ -4409,7 +4409,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -4447,7 +4447,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>15.5</v>
@@ -4485,7 +4485,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>8.6999999999999993</v>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>5</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15">
         <v>5.0999999999999996</v>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16">
         <v>4.2</v>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17">
         <v>5.5</v>
@@ -4675,7 +4675,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B18">
         <v>5.6</v>
@@ -4713,7 +4713,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
